--- a/Exam/gymtrackerpro/lib/schema/__tests__/wbt/utils/emailRegexWbt-wbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/wbt/utils/emailRegexWbt-wbt-form.xlsx
@@ -214,7 +214,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-18</t>
+    <t>SCHEMA-20</t>
   </si>
   <si>
     <t>100%</t>
